--- a/data/trans_orig/P33_1_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P33_1_2023-Clase-trans_orig.xlsx
@@ -489,7 +489,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Número medio de horas que duerme habitualmente al día entre semana</t>
+          <t>Número medio de horas que duerme habitualmente al día entre semana (tasa de respuesta: 97,4%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,92; 7,08</t>
+          <t>6,91; 7,08</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,9; 7,06</t>
+          <t>6,89; 7,06</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,93; 7,05</t>
+          <t>6,93; 7,04</t>
         </is>
       </c>
     </row>
@@ -621,12 +621,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,01; 7,19</t>
+          <t>7,0; 7,19</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,87; 7,05</t>
+          <t>6,87; 7,06</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -671,17 +671,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,9; 7,75</t>
+          <t>6,89; 7,74</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,81; 7,07</t>
+          <t>6,81; 7,08</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,9; 7,67</t>
+          <t>6,91; 7,68</t>
         </is>
       </c>
     </row>
@@ -721,17 +721,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,02; 7,18</t>
+          <t>7,02; 7,19</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,39; 6,95</t>
+          <t>6,37; 6,95</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,64; 7,05</t>
+          <t>6,62; 7,05</t>
         </is>
       </c>
     </row>
@@ -831,7 +831,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7,23; 7,42</t>
+          <t>7,23; 7,41</t>
         </is>
       </c>
     </row>
@@ -871,12 +871,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>7,09; 7,39</t>
+          <t>7,1; 7,45</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6,73; 7,01</t>
+          <t>6,74; 7,01</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">

--- a/data/trans_orig/P33_1_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P33_1_2023-Clase-trans_orig.xlsx
@@ -548,7 +548,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>7,0</t>
+          <t>7,03</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -558,7 +558,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6,99</t>
+          <t>7,01</t>
         </is>
       </c>
     </row>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,91; 7,08</t>
+          <t>6,94; 7,11</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,89; 7,06</t>
+          <t>6,9; 7,07</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,93; 7,04</t>
+          <t>6,94; 7,06</t>
         </is>
       </c>
     </row>
@@ -598,17 +598,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>7,1</t>
+          <t>7,12</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6,96</t>
+          <t>6,97</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7,04</t>
+          <t>7,05</t>
         </is>
       </c>
     </row>
@@ -621,17 +621,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,0; 7,19</t>
+          <t>7,02; 7,21</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,87; 7,06</t>
+          <t>6,88; 7,06</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,97; 7,1</t>
+          <t>6,99; 7,11</t>
         </is>
       </c>
     </row>
@@ -648,17 +648,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>7,32</t>
+          <t>6,96</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>6,94</t>
+          <t>6,95</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7,25</t>
+          <t>6,96</t>
         </is>
       </c>
     </row>
@@ -671,17 +671,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,89; 7,74</t>
+          <t>6,86; 7,07</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,81; 7,08</t>
+          <t>6,82; 7,08</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,91; 7,68</t>
+          <t>6,88; 7,05</t>
         </is>
       </c>
     </row>
@@ -698,17 +698,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>7,1</t>
+          <t>7,12</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>6,73</t>
+          <t>6,93</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6,92</t>
+          <t>7,04</t>
         </is>
       </c>
     </row>
@@ -721,17 +721,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,02; 7,19</t>
+          <t>7,04; 7,2</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,37; 6,95</t>
+          <t>6,85; 7,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,62; 7,05</t>
+          <t>6,98; 7,09</t>
         </is>
       </c>
     </row>
@@ -748,17 +748,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>7,12</t>
+          <t>7,1</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6,92</t>
+          <t>6,93</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6,99</t>
+          <t>7,0</t>
         </is>
       </c>
     </row>
@@ -771,24 +771,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,01; 7,23</t>
+          <t>7,0; 7,19</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,85; 6,99</t>
+          <t>6,85; 7,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,93; 7,05</t>
+          <t>6,94; 7,06</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>7,72</t>
+          <t>7,7</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>7,2</t>
+          <t>7,21</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -821,17 +821,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7,46; 7,92</t>
+          <t>7,47; 7,88</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7,12; 7,28</t>
+          <t>7,13; 7,28</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7,23; 7,41</t>
+          <t>7,24; 7,4</t>
         </is>
       </c>
     </row>
@@ -848,12 +848,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>7,18</t>
+          <t>7,12</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>6,94</t>
+          <t>7,01</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -871,17 +871,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>7,1; 7,45</t>
+          <t>7,08; 7,16</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6,74; 7,01</t>
+          <t>6,97; 7,04</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,97; 7,15</t>
+          <t>7,04; 7,09</t>
         </is>
       </c>
     </row>
